--- a/test/list/sukamantri/mekarwangi/list_mekarwangi_2.xlsx
+++ b/test/list/sukamantri/mekarwangi/list_mekarwangi_2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\dds req\list\sukamantri\mekarwangi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\sukamantri\mekarwangi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8E4C958-A549-48EA-B70C-3342BD9A853F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55994DA0-97D3-4CD2-8DB8-3C381DE46B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="181">
   <si>
     <t>nama</t>
   </si>
@@ -97,216 +97,6 @@
     <t>014</t>
   </si>
   <si>
-    <t>Lampu jalan di depan rumah saya tidak menyala ketika malam.</t>
-  </si>
-  <si>
-    <t>Jalan di sekitar lingkungan kami berlubang dan perlu diperbaiki.</t>
-  </si>
-  <si>
-    <t>Sampah di taman umum tidak dibersihkan secara teratur.</t>
-  </si>
-  <si>
-    <t>Sistem drainase di daerah kami tidak berfungsi dengan baik saat hujan.</t>
-  </si>
-  <si>
-    <t>Ada kebisingan berlebihan dari pabrik yang mengganggu kenyamanan tinggal kami.</t>
-  </si>
-  <si>
-    <t>Fasilitas olahraga seperti lapangan sepak bola dan lapangan basket rusak dan tidak diperbaiki.</t>
-  </si>
-  <si>
-    <t>Tidak ada tempat penampungan sampah yang cukup di sekitar kami.</t>
-  </si>
-  <si>
-    <t>Air minum dari kran di rumah kami terasa kotor dan berbau.</t>
-  </si>
-  <si>
-    <t>Sekolah setempat kurang memadai dalam menyediakan fasilitas pendidikan yang memadai.</t>
-  </si>
-  <si>
-    <t>Gang-gang di lingkungan kami tidak terawat dan menjadi sarang nyamuk.</t>
-  </si>
-  <si>
-    <t>Perluasan jalan di sekitar kami menyebabkan kemacetan lalu lintas yang parah.</t>
-  </si>
-  <si>
-    <t>Kualitas udara di lingkungan kami buruk karena polusi kendaraan.</t>
-  </si>
-  <si>
-    <t>Rute angkutan umum ke daerah kami tidak memadai untuk masyarakat.</t>
-  </si>
-  <si>
-    <t>Listrik sering mati dan pemadaman berlangsung lama di lingkungan kami.</t>
-  </si>
-  <si>
-    <t>Tidak ada fasilitas kesehatan yang memadai di dekat tempat tinggal kami.</t>
-  </si>
-  <si>
-    <t>Tingkat kejahatan di lingkungan kami meningkat dan perlu keamanan yang lebih baik.</t>
-  </si>
-  <si>
-    <t>Tidak ada tempat bermain untuk anak-anak di sekitar kami.</t>
-  </si>
-  <si>
-    <t>Kualitas air di sungai atau danau terdekat tercemar dan perlu diperbaiki.</t>
-  </si>
-  <si>
-    <t>Ruang publik seperti taman dan area hijau tidak dirawat dengan baik.</t>
-  </si>
-  <si>
-    <t>Kualitas penerangan di jalan-jalan kami buruk dan perlu ditingkatkan.</t>
-  </si>
-  <si>
-    <t>Kurangnya tempat parkir yang memadai di sekitar toko dan pusat perbelanjaan.</t>
-  </si>
-  <si>
-    <t>Kurangnya lapangan kerja di lingkungan kami membuat ekonomi warga sulit.</t>
-  </si>
-  <si>
-    <t>Internet di daerah kami tidak stabil dan sering putus.</t>
-  </si>
-  <si>
-    <t>Tidak adanya aksesibilitas bagi orang dengan kebutuhan khusus di tempat umum.</t>
-  </si>
-  <si>
-    <t>Binatang liar seperti anjing liar menjadi masalah di lingkungan kami.</t>
-  </si>
-  <si>
-    <t>Tidak ada jalur pejalan kaki yang aman di sekitar jalan-jalan utama.</t>
-  </si>
-  <si>
-    <t>Tidak adanya ruang terbuka hijau yang cukup di dekat tempat tinggal kami.</t>
-  </si>
-  <si>
-    <t>Tidak ada layanan angkutan umum pada larut malam di wilayah kami.</t>
-  </si>
-  <si>
-    <t>Bangunan yang ditinggalkan dan tidak terawat di sekitar kami menjadi tempat tinggal bagi tikus dan serangga.</t>
-  </si>
-  <si>
-    <t>Kurangnya tempat ibadah yang memadai di daerah kami.</t>
-  </si>
-  <si>
-    <t>Kurangnya fasilitas belajar yang memadai di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Buku teks dan materi pembelajaran yang digunakan sudah usang dan tidak diperbarui.</t>
-  </si>
-  <si>
-    <t>Tingkat kualitas pengajaran guru di beberapa sekolah rendah.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pendidikan keterampilan hidup yang diajarkan di sekolah.</t>
-  </si>
-  <si>
-    <t>Overcrowding (kepadatan) di kelas-kelas sehingga siswa tidak mendapatkan perhatian yang cukup dari guru.</t>
-  </si>
-  <si>
-    <t>Kurangnya aksesibilitas untuk siswa dengan kebutuhan khusus di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Program kurikulum yang tidak relevan dengan kebutuhan dunia kerja.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan dan sumber daya untuk siswa yang berprestasi akademik.</t>
-  </si>
-  <si>
-    <t>Kurangnya kesempatan untuk terlibat dalam kegiatan ekstrakurikuler.</t>
-  </si>
-  <si>
-    <t>Kurangnya pelatihan dan pembinaan untuk guru baru yang masuk.</t>
-  </si>
-  <si>
-    <t>Kurangnya fasilitas laboratorium ilmiah dan komputer di sekolah kami.</t>
-  </si>
-  <si>
-    <t>Kualitas makanan di kantin sekolah kami tidak sehat dan tidak bergizi.</t>
-  </si>
-  <si>
-    <t>Banyak siswa yang melakukan pelecehan atau kekerasan di lingkungan sekolah.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan dan pemahaman bagi siswa dengan masalah kesehatan mental.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pengembangan keterampilan kepemimpinan dan kolaborasi di sekolah.</t>
-  </si>
-  <si>
-    <t>Banyaknya kegiatan pengajaran yang terlalu terfokus pada tes dan bukan pada pemahaman konsep.</t>
-  </si>
-  <si>
-    <t>Kurangnya perhatian terhadap seni dan musik di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Tidak adanya program bantuan atau beasiswa bagi siswa yang kurang mampu secara finansial.</t>
-  </si>
-  <si>
-    <t>Kurangnya guru yang berkualitas dan terlatih di beberapa sekolah pedesaan.</t>
-  </si>
-  <si>
-    <t>Kurangnya sarana transportasi bagi siswa yang tinggal di daerah terpencil.</t>
-  </si>
-  <si>
-    <t>Tingkat disiplin yang rendah di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Tidak adanya pendekatan individual dalam pembelajaran bagi siswa dengan kecepatan belajar yang berbeda.</t>
-  </si>
-  <si>
-    <t>Kurangnya kesempatan untuk berpartisipasi dalam pertukaran pelajar atau program internasional.</t>
-  </si>
-  <si>
-    <t>Kurangnya keterlibatan orang tua dalam pendidikan anak-anak mereka.</t>
-  </si>
-  <si>
-    <t>Tidak adanya konseling karir yang memadai untuk siswa-siswa kami.</t>
-  </si>
-  <si>
-    <t>Kurangnya penekanan pada pendidikan karakter dan etika di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Sistem penilaian yang tidak adil dan kurang transparan.</t>
-  </si>
-  <si>
-    <t>Kurangnya pembaruan teknologi pendidikan di sekolah-sekolah kami.</t>
-  </si>
-  <si>
-    <t>Banyaknya siswa yang putus sekolah atau tidak melanjutkan pendidikan ke jenjang yang lebih tinggi.</t>
-  </si>
-  <si>
-    <t>Tidak adanya program vokasional yang memadai untuk siswa yang tidak melanjutkan ke perguruan tinggi.</t>
-  </si>
-  <si>
-    <t>Kurangnya sarana perpustakaan yang memadai di beberapa sekolah.</t>
-  </si>
-  <si>
-    <t>Kurangnya perhatian pada pendidikan inklusif untuk siswa dengan kebutuhan khusus.</t>
-  </si>
-  <si>
-    <t>Kurangnya pemahaman tentang pentingnya pendidikan seksual yang komprehensif.</t>
-  </si>
-  <si>
-    <t>Kurangnya pelatihan penggunaan teknologi bagi guru dan siswa.</t>
-  </si>
-  <si>
-    <t>Kurangnya program pendidikan tentang keberlanjutan dan lingkungan hidup.</t>
-  </si>
-  <si>
-    <t>Ketidakadilan dalam alokasi dana pendidikan antara daerah perkotaan dan pedesaan.</t>
-  </si>
-  <si>
-    <t>Kurangnya transparansi dalam penggunaan dana pendidikan.</t>
-  </si>
-  <si>
-    <t>Kurangnya pembinaan keterampilan kewirausahaan bagi siswa.</t>
-  </si>
-  <si>
-    <t>Kurangnya dukungan untuk pendidikan seni dan budaya.</t>
-  </si>
-  <si>
-    <t>Tidak adanya akses internet yang memadai di sekolah-sekolah kami.</t>
-  </si>
-  <si>
     <t>Kurangnya penanganan kasus bullying dan kekerasan di sekolah secara tegas.</t>
   </si>
   <si>
@@ -322,274 +112,463 @@
     <t>Tidak adanya program pendidikan tentang keuangan pribadi dan pengelolaan uang.</t>
   </si>
   <si>
-    <t>2023-07-11</t>
-  </si>
-  <si>
-    <t>2023-07-12</t>
-  </si>
-  <si>
-    <t>2023-07-13</t>
-  </si>
-  <si>
-    <t>2023-07-14</t>
-  </si>
-  <si>
-    <t>2023-07-15</t>
-  </si>
-  <si>
-    <t>2023-07-17</t>
-  </si>
-  <si>
-    <t>2023-07-18</t>
-  </si>
-  <si>
-    <t>2023-07-19</t>
-  </si>
-  <si>
-    <t>2023-07-20</t>
-  </si>
-  <si>
-    <t>2023-07-21</t>
-  </si>
-  <si>
-    <t>2023-07-22</t>
-  </si>
-  <si>
-    <t>2023-07-24</t>
-  </si>
-  <si>
-    <t>2023-07-25</t>
-  </si>
-  <si>
-    <t>N. PATONAH</t>
-  </si>
-  <si>
-    <t>DIDA YUNIAR</t>
-  </si>
-  <si>
-    <t>REIHAN ENDI SUANDI</t>
-  </si>
-  <si>
-    <t>MUHAMAD SUDARSONO</t>
-  </si>
-  <si>
-    <t>SITI AISAH</t>
-  </si>
-  <si>
-    <t>ALIF GUMILANG</t>
-  </si>
-  <si>
-    <t>ELSA RAHMA SALSABILA</t>
-  </si>
-  <si>
-    <t>YOSEP BAHTIAR</t>
-  </si>
-  <si>
-    <t>SIDIK</t>
-  </si>
-  <si>
-    <t>IRUN RUNTINI</t>
-  </si>
-  <si>
-    <t>ALVIN ALVIANSYAH</t>
-  </si>
-  <si>
-    <t>ISMAIL</t>
-  </si>
-  <si>
-    <t>YATI JUMIATI</t>
-  </si>
-  <si>
-    <t>MUHAMAD FACHRUL NOER ARIFIN</t>
-  </si>
-  <si>
-    <t>USMAN</t>
-  </si>
-  <si>
-    <t>NETA ERYANTI</t>
-  </si>
-  <si>
-    <t>GIAN PERMANA</t>
-  </si>
-  <si>
-    <t>RIANSYAH</t>
-  </si>
-  <si>
-    <t>EMAH</t>
-  </si>
-  <si>
-    <t>DAERAH</t>
-  </si>
-  <si>
-    <t>IMAN</t>
-  </si>
-  <si>
-    <t>SUSILAWATI</t>
-  </si>
-  <si>
-    <t>EUIS MILA MUPIDAH</t>
-  </si>
-  <si>
-    <t>AI PIDATUL BARIAH</t>
-  </si>
-  <si>
-    <t>WAWAN</t>
-  </si>
-  <si>
-    <t>YANTI</t>
-  </si>
-  <si>
-    <t>PAJAR MEINUDIN</t>
-  </si>
-  <si>
-    <t>PUTRI MAULIDA</t>
-  </si>
-  <si>
-    <t>ABDULAH</t>
-  </si>
-  <si>
-    <t>JUJU JULAEHA</t>
-  </si>
-  <si>
-    <t>ELIS SAFITRI</t>
-  </si>
-  <si>
-    <t>VIA SILVIA</t>
-  </si>
-  <si>
-    <t>DEDEN ABDURAHMAN</t>
-  </si>
-  <si>
-    <t>WATINI</t>
-  </si>
-  <si>
-    <t>AFIATUL MUDHALIFAH</t>
-  </si>
-  <si>
-    <t>AZIZ MAULANA</t>
-  </si>
-  <si>
-    <t>ALWY MUIZ ABDURAHMAN</t>
-  </si>
-  <si>
-    <t>ARIP</t>
-  </si>
-  <si>
-    <t>ARKAN RAPIP MAULID</t>
-  </si>
-  <si>
-    <t>DIKA DJULIANA</t>
-  </si>
-  <si>
-    <t>ILAH</t>
-  </si>
-  <si>
-    <t>JUNAEDI</t>
-  </si>
-  <si>
-    <t>NINING MARSINI</t>
-  </si>
-  <si>
-    <t>IMAM SEPTIANSYAH</t>
-  </si>
-  <si>
-    <t>RISMA ZULIA NINGSIH</t>
-  </si>
-  <si>
-    <t>KARSITI</t>
-  </si>
-  <si>
-    <t>AMINAH</t>
-  </si>
-  <si>
-    <t>PIAN RAMDANI</t>
+    <t xml:space="preserve">Mekarwangi  </t>
+  </si>
+  <si>
+    <t>Rinduwangi</t>
+  </si>
+  <si>
+    <t>Lebakwangi</t>
+  </si>
+  <si>
+    <t>Cikerenceng</t>
+  </si>
+  <si>
+    <t>Pajagan</t>
+  </si>
+  <si>
+    <t>Harga kebutuhan pokok terus meroket, sulit untuk mencukupi.</t>
+  </si>
+  <si>
+    <t>Pengangguran tinggi, sulit mencari pekerjaan yang layak.</t>
+  </si>
+  <si>
+    <t>Upah minimum belum cukup untuk memenuhi kebutuhan hidup.</t>
+  </si>
+  <si>
+    <t>Sulitnya akses kepada layanan kesehatan karena biaya yang tinggi.</t>
+  </si>
+  <si>
+    <t>Pendidikan berkualitas sulit dijangkau akibat biaya tinggi.</t>
+  </si>
+  <si>
+    <t>Besarnya beban pajak dan kurangnya manfaat yang dirasakan.</t>
+  </si>
+  <si>
+    <t>Harga sewa tempat tinggal terlalu tinggi di perkotaan.</t>
+  </si>
+  <si>
+    <t>Sulitnya mendapatkan kredit untuk usaha kecil dan menengah.</t>
+  </si>
+  <si>
+    <t>Inflasi yang tidak terkendali menggerus daya beli.</t>
+  </si>
+  <si>
+    <t>Kesenjangan ekonomi antara kaya dan miskin semakin melebar.</t>
+  </si>
+  <si>
+    <t>Harga BBM dan energi terus naik, mengganggu mobilitas.</t>
+  </si>
+  <si>
+    <t>Keterbatasan peluang ekonomi di daerah pedesaan menyulitkan warga.</t>
+  </si>
+  <si>
+    <t>Sulitnya akses modal untuk pertanian modern di desa.</t>
+  </si>
+  <si>
+    <t>Kurangnya lapangan kerja di sektor industri kreatif.</t>
+  </si>
+  <si>
+    <t>Mahalnya biaya transportasi umum merugikan pekerja.</t>
+  </si>
+  <si>
+    <t>Sulitnya memenuhi kebutuhan pensiun di tengah kenaikan biaya hidup.</t>
+  </si>
+  <si>
+    <t>Rendahnya kualitas infrastruktur di beberapa daerah.</t>
+  </si>
+  <si>
+    <t>Hambatan birokrasi dan korupsi menghambat perkembangan usaha.</t>
+  </si>
+  <si>
+    <t>Investasi asing lebih diuntungkan daripada pengusaha lokal.</t>
+  </si>
+  <si>
+    <t>Sulitnya mendapatkan akses permodalan untuk startup.</t>
+  </si>
+  <si>
+    <t>Sistem perpajakan yang rumit dan membingungkan masyarakat.</t>
+  </si>
+  <si>
+    <t>Tingginya biaya produksi menghambat pertumbuhan industri.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses ke teknologi modern di kalangan masyarakat.</t>
+  </si>
+  <si>
+    <t>Kurangnya dukungan untuk pelatihan keterampilan dari pemerintah terhadap masyarakat.</t>
+  </si>
+  <si>
+    <t>Sulitnya mengakses layanan keuangan seperti kredit usaha.</t>
+  </si>
+  <si>
+    <t>Krisis ekonomi membuat banyak usaha gulung tikar dan ekonomi sulit.</t>
+  </si>
+  <si>
+    <t>Kurangnya diversifikasi ekonomi mengandalkan sektor tertentu.</t>
+  </si>
+  <si>
+    <t>Harga properti yang tinggi sulit dijangkau generasi muda.</t>
+  </si>
+  <si>
+    <t>Mahalnya biaya komunikasi dan akses internet yang terbatas.</t>
+  </si>
+  <si>
+    <t>Sulitnya mengakses pasar ekspor bagi para pelaku usaha kecil.</t>
+  </si>
+  <si>
+    <t>Jalan berlubang menyebabkan kerusakan kendaraan masyarakat.</t>
+  </si>
+  <si>
+    <t>Tidak ada akses air bersih di daerah kami menyulitkan warga.</t>
+  </si>
+  <si>
+    <t>Listrik sering mati, mengganggu aktivitas sehari-hari.</t>
+  </si>
+  <si>
+    <t>Jembatan rusak menghambat mobilitas warga desa yang berlalu lalang.</t>
+  </si>
+  <si>
+    <t>Transportasi umum tidak terjangkau dan tidak nyaman.</t>
+  </si>
+  <si>
+    <t>Drainase buruk menyebabkan banjir saat hujan deras melanda.</t>
+  </si>
+  <si>
+    <t>Fasilitas kesehatan minim, sulit mendapatkan perawatan.</t>
+  </si>
+  <si>
+    <t>Tidak ada akses internet di daerah pedesaan membuat warga kesulitan.</t>
+  </si>
+  <si>
+    <t>Sekolah dalam kondisi rusak, kurang memadai bagi masyarakat.</t>
+  </si>
+  <si>
+    <t>Tempat sampah jarang disediakan, lingkungan kotor.</t>
+  </si>
+  <si>
+    <t>Kereta api sering terlambat, merugikan para penumpang.</t>
+  </si>
+  <si>
+    <t>Tidak ada tempat rekreasi atau taman di sekitar desa.</t>
+  </si>
+  <si>
+    <t>Kualitas udara buruk karena minimnya pohon dan vegetasi.</t>
+  </si>
+  <si>
+    <t>Jalur pejalan kaki tidak aman untuk digunakan bagi warga.</t>
+  </si>
+  <si>
+    <t>Kurangnya lampu jalan membuat malam hari gelap dan rawan.</t>
+  </si>
+  <si>
+    <t>Tidak ada sarana olahraga atau lapangan untuk warga.</t>
+  </si>
+  <si>
+    <t>Fasilitas perbelanjaan terbatas, harus pergi jauh untuk belanja.</t>
+  </si>
+  <si>
+    <t>Kerusakan infrastruktur menyulitkan petani dalam mengangkut hasil pertanian.</t>
+  </si>
+  <si>
+    <t>Keterbatasan tempat parkir di pusat desa kami sangat menyulitkan.</t>
+  </si>
+  <si>
+    <t>kendaraan umum yang sulit dijumpai di wilayah terpencil.</t>
+  </si>
+  <si>
+    <t>Kualitas jaringan telepon seluler buruk di beberapa area.</t>
+  </si>
+  <si>
+    <t>Minimnya jalur sepeda membuat sulit bagi pengendara sepeda.</t>
+  </si>
+  <si>
+    <t>kondisi jalan yang kumuh dan tidak terawat rawan-.</t>
+  </si>
+  <si>
+    <t>Kelistrikan sering terganggu akibat cuaca ekstrem.</t>
+  </si>
+  <si>
+    <t>Pembangunan trotoar yang tidak merata dan berbahaya.</t>
+  </si>
+  <si>
+    <t>Tidak ada jalur khusus transportasi umum, menyebabkan kemacetan.</t>
+  </si>
+  <si>
+    <t>Tidak ada tempat penampungan untuk hewan jalanan di jalan.</t>
+  </si>
+  <si>
+    <t>Pipa air tua sering bocor dan mengganggu pasokan air.</t>
+  </si>
+  <si>
+    <t>Keterbatasan aksesibilitas bagi penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Minimnya tempat parkir untuk kendaraan umum di tempat kami.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan pendapatan dan kesenjangan sosial yang semakin lebar, menciptakan keresahan di kalangan masyarakat.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap layanan kesehatan berkualitas, membuat banyak orang kesulitan mendapatkan perawatan yang dibutuhkan.</t>
+  </si>
+  <si>
+    <t>Kurangnya lapangan kerja dan peluang ekonomi yang memadai, meningkatkan tingkat pengangguran dan ketidakpastian pekerjaan.</t>
+  </si>
+  <si>
+    <t>Sistem pendidikan yang tidak merata dan kurang berkualitas, menghambat kemajuan sosial dan ekonomi bagi sebagian masyarakat.</t>
+  </si>
+  <si>
+    <t>Kurangnya perhatian terhadap isu lingkungan dan keberlanjutan, menciptakan ketidakpastian akan masa depan lingkungan hidup.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>SOLIHIN</t>
+  </si>
+  <si>
+    <t>ENTIN</t>
+  </si>
+  <si>
+    <t>SARJONO</t>
+  </si>
+  <si>
+    <t>YUMYATI</t>
+  </si>
+  <si>
+    <t>YESCAL MAULANA</t>
+  </si>
+  <si>
+    <t>JAKA</t>
+  </si>
+  <si>
+    <t>EROH</t>
+  </si>
+  <si>
+    <t>IBAD BADRIYA</t>
+  </si>
+  <si>
+    <t>YEYEN YUNINGSIH</t>
+  </si>
+  <si>
+    <t>DAHYA</t>
+  </si>
+  <si>
+    <t>WIWIN</t>
+  </si>
+  <si>
+    <t>ENJANG AQIL</t>
+  </si>
+  <si>
+    <t>PATIMAH</t>
+  </si>
+  <si>
+    <t>ERO</t>
+  </si>
+  <si>
+    <t>KONIMAH</t>
+  </si>
+  <si>
+    <t>YOYON</t>
+  </si>
+  <si>
+    <t>AGUN AGUSTIANA</t>
+  </si>
+  <si>
+    <t>YANI</t>
+  </si>
+  <si>
+    <t>MISNAH</t>
+  </si>
+  <si>
+    <t>ISTIKOMAH</t>
+  </si>
+  <si>
+    <t>MUHAMAD</t>
+  </si>
+  <si>
+    <t>MIMIN</t>
+  </si>
+  <si>
+    <t>MIFTAH FARID</t>
+  </si>
+  <si>
+    <t>HERNIAWATI</t>
+  </si>
+  <si>
+    <t>AHYAR</t>
+  </si>
+  <si>
+    <t>SURYATI</t>
+  </si>
+  <si>
+    <t>RISA SITI NURFAZRIAH</t>
+  </si>
+  <si>
+    <t>AGI MAULANA YUSUP</t>
   </si>
   <si>
     <t>ABDUL</t>
   </si>
   <si>
-    <t>ATIN</t>
-  </si>
-  <si>
-    <t>BAIM</t>
-  </si>
-  <si>
-    <t>SITI ROBIAH ADAWIYAH</t>
-  </si>
-  <si>
-    <t>HUSNAN</t>
-  </si>
-  <si>
-    <t>ISAH</t>
-  </si>
-  <si>
-    <t>YUNUS</t>
-  </si>
-  <si>
-    <t>IMRON</t>
-  </si>
-  <si>
-    <t>YAKUB</t>
-  </si>
-  <si>
-    <t>EROH</t>
-  </si>
-  <si>
-    <t>SALEH</t>
-  </si>
-  <si>
-    <t>EDAH</t>
-  </si>
-  <si>
-    <t>ABDUL ROUP</t>
-  </si>
-  <si>
-    <t>JAJANG NASRULOH</t>
-  </si>
-  <si>
-    <t>AYUB</t>
-  </si>
-  <si>
-    <t>ACAH</t>
-  </si>
-  <si>
-    <t>DARUSALAM</t>
-  </si>
-  <si>
-    <t>HUSEN</t>
-  </si>
-  <si>
-    <t>FITRIA</t>
-  </si>
-  <si>
-    <t>RIZAL FAHRI</t>
-  </si>
-  <si>
-    <t>RIMA RAHMIATUL HUSNA</t>
-  </si>
-  <si>
-    <t>RIDO RAMADANI</t>
-  </si>
-  <si>
-    <t>ESO</t>
-  </si>
-  <si>
-    <t>NURYANAH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mekarwangi  </t>
-  </si>
-  <si>
-    <t>Rinduwangi</t>
-  </si>
-  <si>
-    <t>Lebakwangi</t>
-  </si>
-  <si>
-    <t>Cikerenceng</t>
-  </si>
-  <si>
-    <t>Pajagan</t>
+    <t>SURSILAH</t>
+  </si>
+  <si>
+    <t>TARMI</t>
+  </si>
+  <si>
+    <t>JAENUDIN</t>
+  </si>
+  <si>
+    <t>JURIAH</t>
+  </si>
+  <si>
+    <t>FIKHA SALSA AWALIYAH</t>
+  </si>
+  <si>
+    <t>FIKHRI MUHAMAD ARBANI</t>
+  </si>
+  <si>
+    <t>MUMU MUHAEMIN</t>
+  </si>
+  <si>
+    <t>RATNASARI</t>
+  </si>
+  <si>
+    <t>JULFA LATIFATUL FUADAH</t>
+  </si>
+  <si>
+    <t>RINA SRIMULYANI</t>
+  </si>
+  <si>
+    <t>IRUN</t>
+  </si>
+  <si>
+    <t>ADE HAMDUN NAWAWI</t>
+  </si>
+  <si>
+    <t>MUHAMMAD HASBY NAWAWI</t>
+  </si>
+  <si>
+    <t>AAN ANDRIANAH</t>
+  </si>
+  <si>
+    <t>SHEILA OCTAVIA</t>
+  </si>
+  <si>
+    <t>JIBRIL BARAKAH</t>
+  </si>
+  <si>
+    <t>AYET YETI</t>
+  </si>
+  <si>
+    <t>DINA TAWAKALNI</t>
+  </si>
+  <si>
+    <t>IRVAN NUGRAHA</t>
+  </si>
+  <si>
+    <t>RIAN HERMAWAN</t>
+  </si>
+  <si>
+    <t>RANI MAHARANI</t>
+  </si>
+  <si>
+    <t>RAFLI SYAKIR HERMAWAN</t>
+  </si>
+  <si>
+    <t>IWAN RIZKI MAULIDANI</t>
+  </si>
+  <si>
+    <t>DAWUD</t>
+  </si>
+  <si>
+    <t>DESI SARASTUTI</t>
+  </si>
+  <si>
+    <t>DZIKRA MUHAMAD KHANAFI</t>
+  </si>
+  <si>
+    <t>DALFA ZAHRA ASYIFA</t>
+  </si>
+  <si>
+    <t>AHMAD</t>
+  </si>
+  <si>
+    <t>ENUR</t>
+  </si>
+  <si>
+    <t>WAFA NUR ADILLAH</t>
+  </si>
+  <si>
+    <t>RIZKY NUR HIDAYAT</t>
+  </si>
+  <si>
+    <t>KUSDI</t>
+  </si>
+  <si>
+    <t>ANAH</t>
+  </si>
+  <si>
+    <t>TATANG</t>
+  </si>
+  <si>
+    <t>HERNAWATI</t>
+  </si>
+  <si>
+    <t>SAILA ALIKA PUTRI</t>
+  </si>
+  <si>
+    <t>ADIT RIANA</t>
+  </si>
+  <si>
+    <t>SALMAH</t>
+  </si>
+  <si>
+    <t>AGUN SRI GUNAWAN</t>
+  </si>
+  <si>
+    <t>KOKOM KOMALASARI</t>
+  </si>
+  <si>
+    <t>REVILANI NAZIRA GUNAWAN</t>
+  </si>
+  <si>
+    <t>2023-08-15</t>
+  </si>
+  <si>
+    <t>2023-08-16</t>
+  </si>
+  <si>
+    <t>2023-08-17</t>
+  </si>
+  <si>
+    <t>2023-08-18</t>
+  </si>
+  <si>
+    <t>2023-08-19</t>
+  </si>
+  <si>
+    <t>2023-08-21</t>
+  </si>
+  <si>
+    <t>2023-08-22</t>
+  </si>
+  <si>
+    <t>2023-08-23</t>
   </si>
 </sst>
 </file>
@@ -1021,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1032,18 +1011,18 @@
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>003</v>
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>014</v>
       </c>
       <c r="G2" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H2" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -1051,29 +1030,29 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F3" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>003</v>
       </c>
-      <c r="F3" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
-      </c>
       <c r="G3" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -1081,29 +1060,29 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>003</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="G4" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -1111,14 +1090,14 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -1126,14 +1105,14 @@
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="G5" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -1141,29 +1120,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>004</v>
       </c>
       <c r="F6" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>002</v>
       </c>
       <c r="G6" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -1171,29 +1150,29 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>015</v>
       </c>
       <c r="F7" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>012</v>
       </c>
       <c r="G7" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -1201,10 +1180,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1216,14 +1195,14 @@
       </c>
       <c r="F8" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>012</v>
       </c>
       <c r="G8" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -1231,29 +1210,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="D9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>011</v>
       </c>
       <c r="F9" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>005</v>
       </c>
       <c r="G9" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -1261,29 +1240,29 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>99</v>
+        <v>173</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E10" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>009</v>
       </c>
-      <c r="F10" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
-      </c>
       <c r="G10" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -1291,10 +1270,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1302,18 +1281,18 @@
       </c>
       <c r="E11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>015</v>
       </c>
       <c r="F11" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>009</v>
       </c>
       <c r="G11" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -1321,18 +1300,18 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="D12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Pajagan</v>
       </c>
       <c r="E12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>001</v>
       </c>
       <c r="F12" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1343,7 +1322,7 @@
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H12" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -1351,29 +1330,29 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>007</v>
       </c>
       <c r="F13" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="G13" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1381,10 +1360,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1396,14 +1375,14 @@
       </c>
       <c r="F14" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>007</v>
       </c>
       <c r="G14" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1411,10 +1390,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="D15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1426,14 +1405,14 @@
       </c>
       <c r="F15" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>004</v>
       </c>
       <c r="G15" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1441,10 +1420,10 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1452,18 +1431,18 @@
       </c>
       <c r="E16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>011</v>
       </c>
       <c r="F16" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>008</v>
       </c>
       <c r="G16" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1471,29 +1450,29 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="D17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E17" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>012</v>
       </c>
-      <c r="F17" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
-      </c>
       <c r="G17" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
@@ -1501,10 +1480,10 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="D18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1512,18 +1491,18 @@
       </c>
       <c r="E18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="F18" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>001</v>
       </c>
       <c r="G18" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
@@ -1531,29 +1510,29 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="D19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>012</v>
       </c>
       <c r="F19" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="G19" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -1561,10 +1540,10 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="D20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1572,18 +1551,18 @@
       </c>
       <c r="E20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>015</v>
       </c>
       <c r="F20" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>012</v>
       </c>
       <c r="G20" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
@@ -1591,10 +1570,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="D21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1602,18 +1581,18 @@
       </c>
       <c r="E21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>012</v>
       </c>
       <c r="F21" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>005</v>
       </c>
       <c r="G21" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H21" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
@@ -1621,29 +1600,29 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="D22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>005</v>
       </c>
       <c r="F22" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>004</v>
       </c>
       <c r="G22" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
@@ -1651,18 +1630,18 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="D23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>007</v>
       </c>
       <c r="F23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -1673,7 +1652,7 @@
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H23" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
@@ -1681,29 +1660,29 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="D24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>004</v>
       </c>
       <c r="F24" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>012</v>
       </c>
       <c r="G24" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H24" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
@@ -1711,10 +1690,10 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="D25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1722,18 +1701,18 @@
       </c>
       <c r="E25" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>011</v>
       </c>
-      <c r="F25" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
-      </c>
       <c r="G25" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H25" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
@@ -1741,29 +1720,29 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="D26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>003</v>
       </c>
       <c r="F26" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>010</v>
       </c>
       <c r="G26" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H26" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
@@ -1771,29 +1750,29 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>009</v>
       </c>
       <c r="F27" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>006</v>
       </c>
       <c r="G27" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H27" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.35">
@@ -1801,29 +1780,29 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E28" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>002</v>
       </c>
-      <c r="F28" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
-      </c>
       <c r="G28" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.35">
@@ -1831,29 +1810,29 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="D29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>002</v>
       </c>
       <c r="F29" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>006</v>
       </c>
       <c r="G29" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H29" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
@@ -1861,29 +1840,29 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="D30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>013</v>
       </c>
       <c r="F30" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>001</v>
       </c>
       <c r="G30" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H30" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
@@ -1891,10 +1870,10 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>102</v>
+        <v>176</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -1902,134 +1881,134 @@
       </c>
       <c r="E31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>015</v>
       </c>
       <c r="F31" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>013</v>
       </c>
       <c r="G31" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H31" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="D32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>006</v>
       </c>
       <c r="F32" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
+        <v>004</v>
       </c>
       <c r="G32" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H32" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>010</v>
       </c>
       <c r="F33" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>015</v>
       </c>
       <c r="G33" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H33" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="D34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>009</v>
       </c>
       <c r="F34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>011</v>
       </c>
       <c r="G34" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H34" s="3" t="s">
-        <v>55</v>
+      <c r="H34" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B35" s="1" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>008</v>
       </c>
       <c r="F35" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>003</v>
       </c>
       <c r="G35" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>56</v>
+      <c r="H35" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="D36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2037,7 +2016,7 @@
       </c>
       <c r="E36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>002</v>
       </c>
       <c r="F36" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2047,97 +2026,97 @@
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H36" s="3" t="s">
-        <v>57</v>
+      <c r="H36" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="D37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="F37" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>003</v>
       </c>
       <c r="G37" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H37" s="3" t="s">
-        <v>58</v>
+      <c r="H37" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="D38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>014</v>
       </c>
       <c r="F38" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>005</v>
       </c>
       <c r="G38" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H38" s="3" t="s">
-        <v>59</v>
+      <c r="H38" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="D39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>014</v>
       </c>
       <c r="F39" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>009</v>
       </c>
       <c r="G39" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H39" s="3" t="s">
-        <v>60</v>
+      <c r="H39" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2145,26 +2124,26 @@
       </c>
       <c r="E40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>002</v>
       </c>
       <c r="F40" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>002</v>
+        <v>011</v>
       </c>
       <c r="G40" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>61</v>
+      <c r="H40" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B41" s="1" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="D41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2176,49 +2155,49 @@
       </c>
       <c r="F41" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
+        <v>008</v>
       </c>
       <c r="G41" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>62</v>
+      <c r="H41" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>014</v>
       </c>
       <c r="F42" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>011</v>
       </c>
       <c r="G42" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H42" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="D43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2226,7 +2205,7 @@
       </c>
       <c r="E43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>009</v>
       </c>
       <c r="F43" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2236,43 +2215,43 @@
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>64</v>
+      <c r="H43" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B44" s="1" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="D44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>012</v>
       </c>
       <c r="F44" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>006</v>
       </c>
       <c r="G44" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>65</v>
+      <c r="H44" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B45" s="1" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="D45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2280,80 +2259,80 @@
       </c>
       <c r="E45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>003</v>
       </c>
       <c r="F45" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>007</v>
       </c>
       <c r="G45" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>66</v>
+      <c r="H45" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>009</v>
+        <v>008</v>
       </c>
       <c r="F46" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>013</v>
       </c>
       <c r="G46" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>67</v>
+      <c r="H46" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B47" s="1" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="D47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>005</v>
       </c>
       <c r="F47" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>003</v>
       </c>
       <c r="G47" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>68</v>
+      <c r="H47" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="D48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2361,7 +2340,7 @@
       </c>
       <c r="E48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>013</v>
       </c>
       <c r="F48" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2371,43 +2350,43 @@
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>69</v>
+      <c r="H48" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B49" s="1" t="s">
-        <v>105</v>
+        <v>178</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>008</v>
       </c>
       <c r="F49" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
+        <v>007</v>
       </c>
       <c r="G49" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>70</v>
+      <c r="H49" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B50" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="D50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2415,88 +2394,88 @@
       </c>
       <c r="E50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>006</v>
       </c>
       <c r="F50" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>003</v>
       </c>
       <c r="G50" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H50" s="3" t="s">
-        <v>71</v>
+      <c r="H50" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B51" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="D51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E51" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
         <v>012</v>
       </c>
-      <c r="F51" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
-      </c>
       <c r="G51" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B52" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>005</v>
       </c>
       <c r="F52" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>008</v>
       </c>
       <c r="G52" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>73</v>
+      <c r="H52" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B53" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="D53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>011</v>
+        <v>008</v>
       </c>
       <c r="F53" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
@@ -2507,177 +2486,177 @@
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H53" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B54" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>015</v>
       </c>
       <c r="F54" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>011</v>
       </c>
       <c r="G54" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H54" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B55" s="1" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>011</v>
       </c>
       <c r="F55" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>004</v>
       </c>
       <c r="G55" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H55" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B56" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>010</v>
+        <v>007</v>
       </c>
       <c r="F56" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>014</v>
       </c>
       <c r="G56" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H56" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B57" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="D57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
+        <v>015</v>
       </c>
       <c r="F57" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
+        <v>014</v>
       </c>
       <c r="G57" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H57" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B58" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="D58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>001</v>
       </c>
       <c r="F58" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>005</v>
       </c>
       <c r="G58" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H58" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="59" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B59" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D59" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E59" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>012</v>
       </c>
       <c r="F59" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>002</v>
       </c>
       <c r="G59" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H59" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B60" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D60" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -2685,451 +2664,351 @@
       </c>
       <c r="E60" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
+        <v>004</v>
       </c>
       <c r="F60" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>012</v>
+        <v>013</v>
       </c>
       <c r="G60" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H60" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B61" s="1" t="s">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>014</v>
       </c>
       <c r="F61" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>008</v>
       </c>
       <c r="G61" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H61" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B62" s="1" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
+        <v>003</v>
       </c>
       <c r="F62" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
+        <v>014</v>
       </c>
       <c r="G62" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H62" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="63" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B63" s="1" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
+        <v>013</v>
       </c>
       <c r="F63" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
+        <v>013</v>
       </c>
       <c r="G63" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H63" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B64" s="1" t="s">
-        <v>108</v>
+        <v>179</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="D64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>015</v>
+        <v>014</v>
       </c>
       <c r="F64" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>012</v>
       </c>
       <c r="G64" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H64" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
     </row>
     <row r="65" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B65" s="1" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="D65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Rinduwangi</v>
       </c>
       <c r="E65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>013</v>
       </c>
       <c r="F65" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>012</v>
       </c>
       <c r="G65" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H65" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B66" s="1" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>015</v>
       </c>
       <c r="F66" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
+        <v>005</v>
       </c>
       <c r="G66" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H66" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B67" s="1" t="s">
-        <v>108</v>
+        <v>180</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
+        <v>013</v>
       </c>
       <c r="F67" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
+        <v>006</v>
       </c>
       <c r="G67" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H67" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
     </row>
     <row r="68" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B68" s="1" t="s">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>011</v>
       </c>
       <c r="F68" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>012</v>
       </c>
       <c r="G68" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H68" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B69" s="1" t="s">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Lebakwangi</v>
       </c>
       <c r="E69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
+        <v>005</v>
       </c>
       <c r="F69" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>010</v>
+        <v>013</v>
       </c>
       <c r="G69" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H69" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B70" s="1" t="s">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>013</v>
       </c>
       <c r="F70" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
+        <v>014</v>
       </c>
       <c r="G70" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H70" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="71" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B71" s="1" t="s">
-        <v>109</v>
+        <v>180</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
+        <v>Pajagan</v>
       </c>
       <c r="E71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>007</v>
+        <v>002</v>
       </c>
       <c r="F71" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>009</v>
+        <v>003</v>
       </c>
       <c r="G71" s="4" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H71" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
     </row>
     <row r="72" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B72" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D72" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
-      </c>
-      <c r="E72" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
-      </c>
-      <c r="F72" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
-      </c>
-      <c r="G72" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H72" t="s">
-        <v>93</v>
-      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" s="2"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="4"/>
     </row>
     <row r="73" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B73" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="D73" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
-      </c>
-      <c r="E73" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>003</v>
-      </c>
-      <c r="F73" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
-      </c>
-      <c r="G73" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H73" t="s">
-        <v>94</v>
-      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" s="2"/>
+      <c r="E73" s="2"/>
+      <c r="F73" s="2"/>
+      <c r="G73" s="4"/>
     </row>
     <row r="74" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B74" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
-      </c>
-      <c r="E74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
-      </c>
-      <c r="F74" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>007</v>
-      </c>
-      <c r="G74" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H74" t="s">
-        <v>95</v>
-      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" s="2"/>
+      <c r="E74" s="2"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="4"/>
     </row>
     <row r="75" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B75" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
-      </c>
-      <c r="E75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
-      </c>
-      <c r="F75" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
-      </c>
-      <c r="G75" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H75" t="s">
-        <v>96</v>
-      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" s="2"/>
+      <c r="E75" s="2"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="4"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B76" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="D76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
-      </c>
-      <c r="E76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>013</v>
-      </c>
-      <c r="F76" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
-      </c>
-      <c r="G76" s="4" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H76" t="s">
-        <v>97</v>
-      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" s="2"/>
+      <c r="E76" s="2"/>
+      <c r="F76" s="2"/>
+      <c r="G76" s="4"/>
     </row>
     <row r="78" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B78" s="5"/>
@@ -3164,10 +3043,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s">
-        <v>184</v>
+        <v>29</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>19</v>
@@ -3178,7 +3057,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>185</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>13</v>
@@ -3189,7 +3068,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>186</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>14</v>
@@ -3200,7 +3079,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>187</v>
+        <v>32</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>12</v>

--- a/test/list/sukamantri/mekarwangi/list_mekarwangi_2.xlsx
+++ b/test/list/sukamantri/mekarwangi/list_mekarwangi_2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\wdio-dds\test\list\sukamantri\mekarwangi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0835BE56-938F-44B4-9872-B59B93E41B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60C1FA60-DC3C-464F-904C-F11BEA4015A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{4A4170CD-5F29-480B-944E-1B0FEA867C5C}"/>
   </bookViews>
@@ -16,17 +16,28 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="conf" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="144">
   <si>
     <t>nama</t>
   </si>
@@ -160,64 +171,304 @@
     <t>Kurangnya perhatian terhadap isu lingkungan dan keberlanjutan, menciptakan ketidakpastian akan masa depan lingkungan hidup.</t>
   </si>
   <si>
-    <t>AHMAD</t>
-  </si>
-  <si>
-    <t>HERDIANA</t>
-  </si>
-  <si>
-    <t>SAEPUL YUSUP</t>
-  </si>
-  <si>
-    <t>SARI</t>
-  </si>
-  <si>
-    <t>OMOH</t>
-  </si>
-  <si>
-    <t>NANANG</t>
-  </si>
-  <si>
-    <t>PIPIN NURWAIDAH</t>
-  </si>
-  <si>
-    <t>PIKHA SYAMROTUL PUADZAH</t>
-  </si>
-  <si>
-    <t>NANDA SASKIA</t>
-  </si>
-  <si>
-    <t>OHING</t>
-  </si>
-  <si>
-    <t>YULI HERNAWATI</t>
-  </si>
-  <si>
-    <t>MOMON</t>
-  </si>
-  <si>
-    <t>TUTI MULYATI</t>
-  </si>
-  <si>
-    <t>EVAN SATRIA PRAWIRA</t>
-  </si>
-  <si>
-    <t>HILMI MAULANA YUSUF</t>
-  </si>
-  <si>
-    <t>ISKANDAR</t>
-  </si>
-  <si>
-    <t>2023-09-05</t>
-  </si>
-  <si>
-    <t>2023-09-06</t>
-  </si>
-  <si>
-    <t>2023-09-07</t>
-  </si>
-  <si>
-    <t>2023-09-08</t>
+    <t>Banyak masyarakat yang merasa khawatir karena harga pangan yang sering berfluktuasi dan sulit diprediksi.</t>
+  </si>
+  <si>
+    <t>menurut $nama Banyak masyarakat yang merasa khawatir karena harga pangan yang sering berfluktuasi dan sulit diprediksi.</t>
+  </si>
+  <si>
+    <t>Harga kebutuhan pokok naik terus, sulit untuk mencukupi kebutuhan sehari-hari.</t>
+  </si>
+  <si>
+    <t>Pekerjaan sulit dicari, pengangguran meningkat di wilayah ini.</t>
+  </si>
+  <si>
+    <t>Biaya pendidikan mahal, sulit bagi keluarga kurang mampu.</t>
+  </si>
+  <si>
+    <t>Persaingan usaha tidak sehat, usaha kecil sulit bertahan.</t>
+  </si>
+  <si>
+    <t>Banyak produk palsu, merugikan konsumen dan produsen asli.</t>
+  </si>
+  <si>
+    <t>Upah minimum rendah, sulit untuk hidup layak bagi warga.</t>
+  </si>
+  <si>
+    <t>Birokrasi perizinan usaha sulit dan memakan waktu.</t>
+  </si>
+  <si>
+    <t>Ketimpangan sosial dan ekonomi semakin besar, kesenjangan kaya-miskin.</t>
+  </si>
+  <si>
+    <t>Jalan rusak parah, mengganggu kelancaran lalu lintas dan merusak kendaraan.</t>
+  </si>
+  <si>
+    <t>Kemacetan lalu lintas yang parah, menyebabkan waktu tempuh yang lama.</t>
+  </si>
+  <si>
+    <t>Kurangnya perawatan rutin, membuat jalan semakin buruk.</t>
+  </si>
+  <si>
+    <t>Kurangnya penyeberangan pejalan kaki dan fasilitas untuk penyandang disabilitas.</t>
+  </si>
+  <si>
+    <t>Kebutuhan perluasan jalan tidak terpenuhi, menyebabkan kemacetan terus bertambah.</t>
+  </si>
+  <si>
+    <t>Kurangnya penerangan jalan yang memadai, meningkatkan risiko kecelakaan di malam hari.</t>
+  </si>
+  <si>
+    <t>Jalan berlubang yang berbahaya bagi pengendara sepeda motor dan pengguna jalan lainnya.</t>
+  </si>
+  <si>
+    <t>Kurangnya trotoar yang aman, mengancam keselamatan pejalan kaki.</t>
+  </si>
+  <si>
+    <t>Parkir liar yang menghalangi akses jalan dan mengurangi ruang untuk kendaraan.</t>
+  </si>
+  <si>
+    <t>Kurangnya rambu lalu lintas yang jelas dan terawat, membingungkan pengguna jalan.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jalur sepeda yang aman, menghambat pengembangan transportasi berkelanjutan.</t>
+  </si>
+  <si>
+    <t>Kendaraan parkir sembarangan di jalan, menyebabkan kemacetan dan kekacauan.</t>
+  </si>
+  <si>
+    <t>Jalan tidak terlayani saat hujan, menyebabkan banjir dan genangan air.</t>
+  </si>
+  <si>
+    <t>Tidak adanya fasilitas penyeberangan untuk hewan di jalan raya.</t>
+  </si>
+  <si>
+    <t>Maraknya kekerasan dan kriminalitas, menciptakan rasa takut dan tidak aman di lingkungan sekitar.</t>
+  </si>
+  <si>
+    <t>Keterbatasan akses terhadap perumahan yang layak dan terjangkau, menyebabkan masalah perumahan bagi banyak keluarga.</t>
+  </si>
+  <si>
+    <t>Ketidaksetaraan gender yang masih ada dalam berbagai aspek kehidupan, termasuk di tempat kerja dan dalam lingkungan domestik.</t>
+  </si>
+  <si>
+    <t>Tidak adanya jaringan pengaman sosial yang memadai, menyebabkan kelompok rentan sulit mendapatkan dukungan saat menghadapi kesulitan.</t>
+  </si>
+  <si>
+    <t>Isu diskriminasi rasial dan etnis yang terus muncul, menciptakan ketegangan dan konflik di antara berbagai kelompok masyarakat.</t>
+  </si>
+  <si>
+    <t>Jalan tidak ramah lingkungan, tanpa pohon atau taman penyerap polusi.</t>
+  </si>
+  <si>
+    <t>Marka jalan yang pudar atau tidak terlihat jelas, meningkatkan risiko kecelakaan.</t>
+  </si>
+  <si>
+    <t>Kurangnya jalan alternatif untuk mengurangi kepadatan lalu lintas di ruas jalan utama.</t>
+  </si>
+  <si>
+    <t>2023-10-10</t>
+  </si>
+  <si>
+    <t>2023-10-11</t>
+  </si>
+  <si>
+    <t>2023-10-12</t>
+  </si>
+  <si>
+    <t>2023-10-13</t>
+  </si>
+  <si>
+    <t>2023-10-14</t>
+  </si>
+  <si>
+    <t>2023-10-16</t>
+  </si>
+  <si>
+    <t>2023-10-17</t>
+  </si>
+  <si>
+    <t>2023-10-18</t>
+  </si>
+  <si>
+    <t>2023-10-19</t>
+  </si>
+  <si>
+    <t>2023-10-20</t>
+  </si>
+  <si>
+    <t>2023-10-21</t>
+  </si>
+  <si>
+    <t>2023-10-23</t>
+  </si>
+  <si>
+    <t>2023-10-24</t>
+  </si>
+  <si>
+    <t>REZA AL-FHATIH</t>
+  </si>
+  <si>
+    <t>SRI RAHMAWATI</t>
+  </si>
+  <si>
+    <t>ABDUL MISBAH</t>
+  </si>
+  <si>
+    <t>ATRIANI</t>
+  </si>
+  <si>
+    <t>YATI ROSMIATI</t>
+  </si>
+  <si>
+    <t>DIDI KUSNADI</t>
+  </si>
+  <si>
+    <t>UUM MULYATI</t>
+  </si>
+  <si>
+    <t>KIKI BAHRUL ILMI</t>
+  </si>
+  <si>
+    <t>CARSO</t>
+  </si>
+  <si>
+    <t>ETI</t>
+  </si>
+  <si>
+    <t>KOKOM MULYANI</t>
+  </si>
+  <si>
+    <t>WARJA</t>
+  </si>
+  <si>
+    <t>ROHIMAH</t>
+  </si>
+  <si>
+    <t>YATI ROHMAYATI</t>
+  </si>
+  <si>
+    <t>CUNDA</t>
+  </si>
+  <si>
+    <t>ULPAH</t>
+  </si>
+  <si>
+    <t>ADE FAHRUL FAUZI</t>
+  </si>
+  <si>
+    <t>ADE JAENAL ARIPIN</t>
+  </si>
+  <si>
+    <t>YAYAT NURHAYATI</t>
+  </si>
+  <si>
+    <t>RAMADANI ANUGRAH PUTRA</t>
+  </si>
+  <si>
+    <t>IIS RAHMIYATI</t>
+  </si>
+  <si>
+    <t>ABDUL</t>
+  </si>
+  <si>
+    <t>IKAH</t>
+  </si>
+  <si>
+    <t>AJIP APRIANSYAH</t>
+  </si>
+  <si>
+    <t>ROHIM</t>
+  </si>
+  <si>
+    <t>NANI</t>
+  </si>
+  <si>
+    <t>OMAN</t>
+  </si>
+  <si>
+    <t>JULAEHA</t>
+  </si>
+  <si>
+    <t>IDA ROSIDA</t>
+  </si>
+  <si>
+    <t>IKIN ROJIKIN</t>
+  </si>
+  <si>
+    <t>UJU</t>
+  </si>
+  <si>
+    <t>ADILA ROZIKA</t>
+  </si>
+  <si>
+    <t>RIYADHUN NABHAN</t>
+  </si>
+  <si>
+    <t>ELON</t>
+  </si>
+  <si>
+    <t>SALMAH</t>
+  </si>
+  <si>
+    <t>SALMAN</t>
+  </si>
+  <si>
+    <t>ONIH</t>
+  </si>
+  <si>
+    <t>ANDI KURNIAWAN</t>
+  </si>
+  <si>
+    <t>JENAL</t>
+  </si>
+  <si>
+    <t>RISKA WULANDARI</t>
+  </si>
+  <si>
+    <t>DENI JAELANI</t>
+  </si>
+  <si>
+    <t>TARSIM</t>
+  </si>
+  <si>
+    <t>OOH</t>
+  </si>
+  <si>
+    <t>IWAN RIDWAN</t>
+  </si>
+  <si>
+    <t>IMAS MASITOH</t>
+  </si>
+  <si>
+    <t>AGUS SETIAWAN</t>
+  </si>
+  <si>
+    <t>TIAN PRASTIANTI</t>
+  </si>
+  <si>
+    <t>HARUN</t>
+  </si>
+  <si>
+    <t>ENTIN</t>
+  </si>
+  <si>
+    <t>ROSID</t>
+  </si>
+  <si>
+    <t>ETI ROSMAWATI</t>
+  </si>
+  <si>
+    <t>FAIZUL HAQ</t>
+  </si>
+  <si>
+    <t>ZAKI MUBAROX</t>
+  </si>
+  <si>
+    <t>MUKSIN</t>
+  </si>
+  <si>
+    <t>OON</t>
   </si>
 </sst>
 </file>
@@ -225,9 +476,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,14 +505,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -282,17 +525,19 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Mata Uang" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -309,7 +554,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -605,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330EDF8F-AF7E-4CFD-AD2A-76F45302569C}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="14.36328125" style="1" customWidth="1"/>
@@ -646,14 +891,14 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="D2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
+        <v>Cikerenceng</v>
       </c>
       <c r="E2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
@@ -661,14 +906,14 @@
       </c>
       <c r="F2" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>011</v>
       </c>
       <c r="G2" s="3" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
@@ -676,10 +921,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="D3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -691,14 +936,14 @@
       </c>
       <c r="F3" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
+        <v>013</v>
       </c>
       <c r="G3" s="3" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
@@ -706,10 +951,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="D4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
@@ -717,18 +962,18 @@
       </c>
       <c r="E4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
+        <v>002</v>
       </c>
       <c r="F4" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>001</v>
       </c>
       <c r="G4" s="3" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H4" t="s">
-        <v>30</v>
+      <c r="H4" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
@@ -736,29 +981,29 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
+        <v>Pajagan</v>
       </c>
       <c r="E5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
+        <v>012</v>
       </c>
       <c r="F5" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>008</v>
+        <v>012</v>
       </c>
       <c r="G5" s="3" t="str">
         <f>conf!$A$2</f>
         <v xml:space="preserve">Mekarwangi  </v>
       </c>
-      <c r="H5" t="s">
-        <v>31</v>
+      <c r="H5" s="4" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
@@ -766,29 +1011,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E6" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F6" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G6" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="D6" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>012</v>
-      </c>
-      <c r="F6" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
-      </c>
-      <c r="G6" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
@@ -796,29 +1041,29 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D7" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E7" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F7" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G7" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>49</v>
-      </c>
-      <c r="D7" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Pajagan</v>
-      </c>
-      <c r="E7" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
-      </c>
-      <c r="F7" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>013</v>
-      </c>
-      <c r="G7" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H7" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
@@ -826,29 +1071,29 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E8" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>004</v>
+      </c>
+      <c r="F8" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G8" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="D8" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
-      </c>
-      <c r="G8" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H8" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
@@ -856,29 +1101,29 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E9" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F9" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G9" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="D9" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
-      </c>
-      <c r="E9" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
-      </c>
-      <c r="F9" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>005</v>
-      </c>
-      <c r="G9" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H9" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
@@ -886,29 +1131,29 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D10" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E10" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F10" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G10" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D10" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
-      </c>
-      <c r="E10" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>014</v>
-      </c>
-      <c r="F10" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>014</v>
-      </c>
-      <c r="G10" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H10" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -916,29 +1161,29 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E11" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F11" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G11" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H11" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="D11" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Cikerenceng</v>
-      </c>
-      <c r="E11" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>006</v>
-      </c>
-      <c r="F11" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>011</v>
-      </c>
-      <c r="G11" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
@@ -946,29 +1191,29 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G12" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H12" t="s">
         <v>54</v>
-      </c>
-      <c r="D12" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
-      </c>
-      <c r="E12" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>004</v>
-      </c>
-      <c r="F12" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>001</v>
-      </c>
-      <c r="G12" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H12" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
@@ -976,29 +1221,29 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E13" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F13" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G13" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H13" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="D13" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>001</v>
-      </c>
-      <c r="F13" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>003</v>
-      </c>
-      <c r="G13" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H13" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
@@ -1006,29 +1251,29 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E14" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F14" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G14" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H14" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D14" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Lebakwangi</v>
-      </c>
-      <c r="E14" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>002</v>
-      </c>
-      <c r="F14" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>006</v>
-      </c>
-      <c r="G14" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H14" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
@@ -1036,29 +1281,29 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E15" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>009</v>
+      </c>
+      <c r="F15" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G15" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H15" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="D15" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
-      </c>
-      <c r="E15" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>005</v>
-      </c>
-      <c r="F15" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>015</v>
-      </c>
-      <c r="G15" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H15" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
@@ -1066,29 +1311,29 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E16" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F16" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G16" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="D16" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
-        <v>Rinduwangi</v>
-      </c>
-      <c r="E16" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
-        <v>008</v>
-      </c>
-      <c r="F16" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
-        <v>004</v>
-      </c>
-      <c r="G16" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H16" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
@@ -1096,70 +1341,1110 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F17" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G17" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B18" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F18" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G18" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F19" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G19" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B20" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F20" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G20" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B21" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>007</v>
+      </c>
+      <c r="F21" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G21" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H21" t="s">
         <v>63</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D17" s="2" t="str">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F22" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G22" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
         <v>Cikerenceng</v>
       </c>
-      <c r="E17" s="2" t="str">
+      <c r="E23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F23" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G23" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B24" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F24" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>008</v>
+      </c>
+      <c r="G24" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H24" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B25" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F25" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F26" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>010</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B27" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G27" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B28" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G28" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="D29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>015</v>
+      </c>
+      <c r="G29" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G30" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B31" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G31" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F32" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G32" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B33" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F33" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G33" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B34" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E34" s="2" t="str">
         <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
         <v>005</v>
       </c>
-      <c r="F17" s="2" t="str">
-        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+      <c r="F34" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G34" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B35" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F35" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>012</v>
+      </c>
+      <c r="G35" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H35" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
         <v>004</v>
       </c>
-      <c r="G17" s="3" t="str">
-        <f>conf!$A$2</f>
-        <v xml:space="preserve">Mekarwangi  </v>
-      </c>
-      <c r="H17" t="s">
+      <c r="F36" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G36" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H36" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B37" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>008</v>
+      </c>
+      <c r="F37" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>003</v>
+      </c>
+      <c r="G37" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H37" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B38" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F38" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G38" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B39" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F39" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>006</v>
+      </c>
+      <c r="G39" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="D40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F40" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G40" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H40" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>011</v>
+      </c>
+      <c r="F41" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>011</v>
+      </c>
+      <c r="G41" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H41" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="B24" s="4"/>
-      <c r="D24" s="1"/>
-      <c r="F24"/>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B42" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F42" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>002</v>
+      </c>
+      <c r="G42" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B43" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F43" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G43" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H43" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B44" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>014</v>
+      </c>
+      <c r="F44" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G44" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H44" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B45" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F45" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G45" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H45" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>005</v>
+      </c>
+      <c r="F46" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G46" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H46" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>010</v>
+      </c>
+      <c r="F47" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>005</v>
+      </c>
+      <c r="G47" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H47" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F48" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G48" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H48" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="49" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B49" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="D49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F49" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>007</v>
+      </c>
+      <c r="G49" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H49" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B50" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Rinduwangi</v>
+      </c>
+      <c r="E50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>012</v>
+      </c>
+      <c r="F50" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G50" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H50" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B51" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F51" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>004</v>
+      </c>
+      <c r="G51" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H51" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B52" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F52" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G52" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H52" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B53" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>003</v>
+      </c>
+      <c r="F53" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>001</v>
+      </c>
+      <c r="G53" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="54" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B54" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>006</v>
+      </c>
+      <c r="F54" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G54" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H54" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B55" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="D55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Pajagan</v>
+      </c>
+      <c r="E55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>015</v>
+      </c>
+      <c r="F55" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>013</v>
+      </c>
+      <c r="G55" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H55" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B56" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Lebakwangi</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>001</v>
+      </c>
+      <c r="F56" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>009</v>
+      </c>
+      <c r="G56" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H56" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B57" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,4),1)</f>
+        <v>Cikerenceng</v>
+      </c>
+      <c r="E57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),3)</f>
+        <v>002</v>
+      </c>
+      <c r="F57" s="2" t="str">
+        <f ca="1">INDEX(conf!$B$2:$D$16,RANDBETWEEN(1,15),2)</f>
+        <v>014</v>
+      </c>
+      <c r="G57" s="3" t="str">
+        <f>conf!$A$2</f>
+        <v xml:space="preserve">Mekarwangi  </v>
+      </c>
+      <c r="H57" t="s">
+        <v>75</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
